--- a/02_pam/output/stat_results/pairwise_allmetsxtissues.xlsx
+++ b/02_pam/output/stat_results/pairwise_allmetsxtissues.xlsx
@@ -1,1073 +1,1066 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennaekwealor/Documents/Cuscuta_phylo_photosynthesis/02_pam/output/stat_results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BC5D99-FE52-4D40-9AA2-021CD8F00291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="14260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ΦNPQ" sheetId="1" r:id="rId1"/>
+    <sheet name="ΦNPQ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="347">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>C. purpurata</t>
-  </si>
-  <si>
-    <t>Cuscuta</t>
-  </si>
-  <si>
-    <t>Grammica</t>
-  </si>
-  <si>
-    <t>Ipomoea nil</t>
-  </si>
-  <si>
-    <t>Monogynella</t>
-  </si>
-  <si>
-    <t>Flower</t>
-  </si>
-  <si>
-    <t>Haustorium</t>
-  </si>
-  <si>
-    <t>Old</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Seed</t>
-  </si>
-  <si>
-    <t>Seedling</t>
-  </si>
-  <si>
-    <t>Leaf</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1.46224451926888e-06</t>
-  </si>
-  <si>
-    <t>3.75484851835537e-05</t>
-  </si>
-  <si>
-    <t>0.00322478514804319</t>
-  </si>
-  <si>
-    <t>2.72032065263047e-06</t>
-  </si>
-  <si>
-    <t>0.000682800230446674</t>
-  </si>
-  <si>
-    <t>0.0035853107459584</t>
-  </si>
-  <si>
-    <t>0.0337424317618012</t>
-  </si>
-  <si>
-    <t>0.000946866578579858</t>
-  </si>
-  <si>
-    <t>0.273797790863862</t>
-  </si>
-  <si>
-    <t>0.0639842341504868</t>
-  </si>
-  <si>
-    <t>0.121636143927188</t>
-  </si>
-  <si>
-    <t>0.270577440900021</t>
-  </si>
-  <si>
-    <t>0.0725333286055547</t>
-  </si>
-  <si>
-    <t>0.00482992735951079</t>
-  </si>
-  <si>
-    <t>0.137475031612282</t>
-  </si>
-  <si>
-    <t>1.47097950776123e-06</t>
-  </si>
-  <si>
-    <t>1.07032927025925e-05</t>
-  </si>
-  <si>
-    <t>0.000460400327310872</t>
-  </si>
-  <si>
-    <t>2.11978566589768e-06</t>
-  </si>
-  <si>
-    <t>0.260711948605843</t>
-  </si>
-  <si>
-    <t>0.0426950141993282</t>
-  </si>
-  <si>
-    <t>0.000812066078919599</t>
-  </si>
-  <si>
-    <t>0.0242542531115658</t>
-  </si>
-  <si>
-    <t>0.0326718615602025</t>
-  </si>
-  <si>
-    <t>0.0682399260355361</t>
-  </si>
-  <si>
-    <t>0.0253810619291163</t>
-  </si>
-  <si>
-    <t>0.747161188055441</t>
-  </si>
-  <si>
-    <t>0.805296150960781</t>
-  </si>
-  <si>
-    <t>0.248140300967333</t>
-  </si>
-  <si>
-    <t>0.270475818247867</t>
-  </si>
-  <si>
-    <t>0.530169016260407</t>
-  </si>
-  <si>
-    <t>0.601727280265683</t>
-  </si>
-  <si>
-    <t>0.715408972747075</t>
-  </si>
-  <si>
-    <t>0.542534833769019</t>
-  </si>
-  <si>
-    <t>0.000124537132673083</t>
-  </si>
-  <si>
-    <t>0.0113553785340147</t>
-  </si>
-  <si>
-    <t>0.295310767671895</t>
-  </si>
-  <si>
-    <t>3.60403805117689e-05</t>
-  </si>
-  <si>
-    <t>0.0708281954149198</t>
-  </si>
-  <si>
-    <t>9.39412010863675e-10</t>
-  </si>
-  <si>
-    <t>2.96830318319785e-06</t>
-  </si>
-  <si>
-    <t>0.00305740312859448</t>
-  </si>
-  <si>
-    <t>5.52935462450762e-09</t>
-  </si>
-  <si>
-    <t>0.618172914054875</t>
-  </si>
-  <si>
-    <t>0.354970425522269</t>
-  </si>
-  <si>
-    <t>0.00105667010131659</t>
-  </si>
-  <si>
-    <t>0.0863063636144745</t>
-  </si>
-  <si>
-    <t>0.928545186488749</t>
-  </si>
-  <si>
-    <t>4.75945517003654e-06</t>
-  </si>
-  <si>
-    <t>1.08222227784671e-13</t>
-  </si>
-  <si>
-    <t>1.00041042491186e-08</t>
-  </si>
-  <si>
-    <t>0.000255894990943642</t>
-  </si>
-  <si>
-    <t>2.20449604609997e-12</t>
-  </si>
-  <si>
-    <t>0.571517418501662</t>
-  </si>
-  <si>
-    <t>0.0378053388696402</t>
-  </si>
-  <si>
-    <t>4.40128035655464e-06</t>
-  </si>
-  <si>
-    <t>0.351700211712042</t>
-  </si>
-  <si>
-    <t>0.521767683778997</t>
-  </si>
-  <si>
-    <t>6.6613157015166e-09</t>
-  </si>
-  <si>
-    <t>0.00457616268253145</t>
-  </si>
-  <si>
-    <t>4.72199492168867e-07</t>
-  </si>
-  <si>
-    <t>0.000131350929853924</t>
-  </si>
-  <si>
-    <t>0.0152035609481612</t>
-  </si>
-  <si>
-    <t>1.77612330536753e-06</t>
-  </si>
-  <si>
-    <t>0.131552358360585</t>
-  </si>
-  <si>
-    <t>0.0262818412814172</t>
-  </si>
-  <si>
-    <t>0.0168185109680361</t>
-  </si>
-  <si>
-    <t>0.79962028927607</t>
-  </si>
-  <si>
-    <t>0.000347256186511562</t>
-  </si>
-  <si>
-    <t>0.0208140162214639</t>
-  </si>
-  <si>
-    <t>9.67657227515035e-08</t>
-  </si>
-  <si>
-    <t>4.16259318542139e-15</t>
-  </si>
-  <si>
-    <t>5.1850061237932e-10</t>
-  </si>
-  <si>
-    <t>4.47637707085502e-05</t>
-  </si>
-  <si>
-    <t>5.90910229660792e-14</t>
-  </si>
-  <si>
-    <t>0.167408645414639</t>
-  </si>
-  <si>
-    <t>0.00506315070110156</t>
-  </si>
-  <si>
-    <t>1.91277748286349e-07</t>
-  </si>
-  <si>
-    <t>0.747930276947236</t>
-  </si>
-  <si>
-    <t>0.290785232601444</t>
-  </si>
-  <si>
-    <t>2.77336958439926e-10</t>
-  </si>
-  <si>
-    <t>8.79574277838788e-05</t>
-  </si>
-  <si>
-    <t>0.1087268104732</t>
-  </si>
-  <si>
-    <t>3.35955817329655e-09</t>
-  </si>
-  <si>
-    <t>2.91637528332398e-10</t>
-  </si>
-  <si>
-    <t>4.21175833462657e-07</t>
-  </si>
-  <si>
-    <t>0.000712365883286905</t>
-  </si>
-  <si>
-    <t>1.11895842291517e-09</t>
-  </si>
-  <si>
-    <t>0.800575924110083</t>
-  </si>
-  <si>
-    <t>0.105739707082462</t>
-  </si>
-  <si>
-    <t>0.00013707569732857</t>
-  </si>
-  <si>
-    <t>0.292424068289888</t>
-  </si>
-  <si>
-    <t>0.626116350484326</t>
-  </si>
-  <si>
-    <t>6.98436374305867e-07</t>
-  </si>
-  <si>
-    <t>0.17071859982009</t>
-  </si>
-  <si>
-    <t>0.713996372371247</t>
-  </si>
-  <si>
-    <t>0.00284655662765445</t>
-  </si>
-  <si>
-    <t>0.118127855377932</t>
-  </si>
-  <si>
-    <t>4.53517511318093e-06</t>
-  </si>
-  <si>
-    <t>0.000530900968184607</t>
-  </si>
-  <si>
-    <t>0.0291495608465698</t>
-  </si>
-  <si>
-    <t>1.42200803310946e-05</t>
-  </si>
-  <si>
-    <t>0.045143467045902</t>
-  </si>
-  <si>
-    <t>0.746760588338337</t>
-  </si>
-  <si>
-    <t>0.0799855778251784</t>
-  </si>
-  <si>
-    <t>0.00701363182218485</t>
-  </si>
-  <si>
-    <t>0.658060551524371</t>
-  </si>
-  <si>
-    <t>0.00176532299133625</t>
-  </si>
-  <si>
-    <t>0.000454912521722661</t>
-  </si>
-  <si>
-    <t>4.50903578058083e-11</t>
-  </si>
-  <si>
-    <t>0.292183401966117</t>
-  </si>
-  <si>
-    <t>9.23238648557227e-12</t>
-  </si>
-  <si>
-    <t>0.000164671694831804</t>
-  </si>
-  <si>
-    <t>4.29517444158324e-12</t>
-  </si>
-  <si>
-    <t>5.32384811146346e-10</t>
-  </si>
-  <si>
-    <t>2.14020580866425e-06</t>
-  </si>
-  <si>
-    <t>8.44754678691524e-12</t>
-  </si>
-  <si>
-    <t>0.00680034311564503</t>
-  </si>
-  <si>
-    <t>0.000235552287604985</t>
-  </si>
-  <si>
-    <t>1.54909547545767e-07</t>
-  </si>
-  <si>
-    <t>0.302786377256755</t>
-  </si>
-  <si>
-    <t>0.0398461142578602</t>
-  </si>
-  <si>
-    <t>1.08130449890359e-09</t>
-  </si>
-  <si>
-    <t>0.000132267191052863</t>
-  </si>
-  <si>
-    <t>0.00459610250181658</t>
-  </si>
-  <si>
-    <t>3.23260753572081e-06</t>
-  </si>
-  <si>
-    <t>0.0408509225109615</t>
-  </si>
-  <si>
-    <t>0.00427100957637709</t>
-  </si>
-  <si>
-    <t>5.265267887922e-07</t>
-  </si>
-  <si>
-    <t>1.2668714614188e-09</t>
-  </si>
-  <si>
-    <t>1.04858613298135e-07</t>
-  </si>
-  <si>
-    <t>6.1566950977827e-05</t>
-  </si>
-  <si>
-    <t>2.93133086249473e-09</t>
-  </si>
-  <si>
-    <t>0.104913902714394</t>
-  </si>
-  <si>
-    <t>0.00788569009490001</t>
-  </si>
-  <si>
-    <t>1.87432059487337e-05</t>
-  </si>
-  <si>
-    <t>0.876351838786783</t>
-  </si>
-  <si>
-    <t>0.178982716905263</t>
-  </si>
-  <si>
-    <t>2.87683508876676e-07</t>
-  </si>
-  <si>
-    <t>0.0104040463903407</t>
-  </si>
-  <si>
-    <t>0.131055597929021</t>
-  </si>
-  <si>
-    <t>0.000594548340377815</t>
-  </si>
-  <si>
-    <t>0.45408889174505</t>
-  </si>
-  <si>
-    <t>0.104825595798068</t>
-  </si>
-  <si>
-    <t>0.000132183015817012</t>
-  </si>
-  <si>
-    <t>0.336473404241388</t>
-  </si>
-  <si>
-    <t>1.24583199074703e-06</t>
-  </si>
-  <si>
-    <t>9.13538982166457e-06</t>
-  </si>
-  <si>
-    <t>0.000422277068703477</t>
-  </si>
-  <si>
-    <t>1.76887765389534e-06</t>
-  </si>
-  <si>
-    <t>0.248715557993255</t>
-  </si>
-  <si>
-    <t>0.0395972784489365</t>
-  </si>
-  <si>
-    <t>0.000707386940368675</t>
-  </si>
-  <si>
-    <t>0.260644352335804</t>
-  </si>
-  <si>
-    <t>3.07070654414617e-05</t>
-  </si>
-  <si>
-    <t>0.078782147332221</t>
-  </si>
-  <si>
-    <t>0.33177300082611</t>
-  </si>
-  <si>
-    <t>0.0150505102797091</t>
-  </si>
-  <si>
-    <t>0.723133667997695</t>
-  </si>
-  <si>
-    <t>0.276582345707604</t>
-  </si>
-  <si>
-    <t>0.00620822277788642</t>
-  </si>
-  <si>
-    <t>0.314699178785733</t>
-  </si>
-  <si>
-    <t>0.902676513892812</t>
-  </si>
-  <si>
-    <t>0.00279824676031349</t>
-  </si>
-  <si>
-    <t>0.00980658026402619</t>
-  </si>
-  <si>
-    <t>0.0609258017453342</t>
-  </si>
-  <si>
-    <t>0.00354927107955494</t>
-  </si>
-  <si>
-    <t>0.150966706020696</t>
-  </si>
-  <si>
-    <t>0.779002291139313</t>
-  </si>
-  <si>
-    <t>0.262576304927262</t>
-  </si>
-  <si>
-    <t>0.0213698721704374</t>
-  </si>
-  <si>
-    <t>0.662406455712772</t>
-  </si>
-  <si>
-    <t>0.0302471103389535</t>
-  </si>
-  <si>
-    <t>0.171332083545665</t>
-  </si>
-  <si>
-    <t>0.0104455139133138</t>
-  </si>
-  <si>
-    <t>0.668820986575216</t>
-  </si>
-  <si>
-    <t>0.00107779619319593</t>
-  </si>
-  <si>
-    <t>0.0385317347256017</t>
-  </si>
-  <si>
-    <t>0.980578166727473</t>
-  </si>
-  <si>
-    <t>6.42333057935755e-05</t>
-  </si>
-  <si>
-    <t>0.00292638904999341</t>
-  </si>
-  <si>
-    <t>0.0194576661866949</t>
-  </si>
-  <si>
-    <t>2.36871686043055e-10</t>
-  </si>
-  <si>
-    <t>5.25148243921976e-09</t>
-  </si>
-  <si>
-    <t>3.31934835347203e-06</t>
-  </si>
-  <si>
-    <t>3.84495444937986e-10</t>
-  </si>
-  <si>
-    <t>0.00745204038665192</t>
-  </si>
-  <si>
-    <t>0.000398361835084255</t>
-  </si>
-  <si>
-    <t>1.01222354320063e-06</t>
-  </si>
-  <si>
-    <t>0.241075240605813</t>
-  </si>
-  <si>
-    <t>0.0315293043051818</t>
-  </si>
-  <si>
-    <t>1.50679182019293e-08</t>
-  </si>
-  <si>
-    <t>0.000432447971566475</t>
-  </si>
-  <si>
-    <t>0.00705015762429371</t>
-  </si>
-  <si>
-    <t>2.76038881614787e-05</t>
-  </si>
-  <si>
-    <t>0.0400883856671761</t>
-  </si>
-  <si>
-    <t>0.00606925648662256</t>
-  </si>
-  <si>
-    <t>6.49044693113735e-06</t>
-  </si>
-  <si>
-    <t>0.817621083701603</t>
-  </si>
-  <si>
-    <t>0.260160775954813</t>
-  </si>
-  <si>
-    <t>0.252049791564807</t>
-  </si>
-  <si>
-    <t>0.000134099135523838</t>
-  </si>
-  <si>
-    <t>4.94074037949834e-10</t>
-  </si>
-  <si>
-    <t>7.81827085592423e-08</t>
-  </si>
-  <si>
-    <t>8.32760463236945e-05</t>
-  </si>
-  <si>
-    <t>1.12202607884442e-09</t>
-  </si>
-  <si>
-    <t>0.151443071695378</t>
-  </si>
-  <si>
-    <t>0.010745958927152</t>
-  </si>
-  <si>
-    <t>1.67839085728675e-05</t>
-  </si>
-  <si>
-    <t>0.235045951589767</t>
-  </si>
-  <si>
-    <t>1.86550660373235e-07</t>
-  </si>
-  <si>
-    <t>0.0128372525746945</t>
-  </si>
-  <si>
-    <t>0.192144287095634</t>
-  </si>
-  <si>
-    <t>0.000510466173422112</t>
-  </si>
-  <si>
-    <t>0.661425144720851</t>
-  </si>
-  <si>
-    <t>0.153145649878632</t>
-  </si>
-  <si>
-    <t>9.11621418027915e-05</t>
-  </si>
-  <si>
-    <t>0.208211166054674</t>
-  </si>
-  <si>
-    <t>0.823400895912742</t>
-  </si>
-  <si>
-    <t>0.00370715601822831</t>
-  </si>
-  <si>
-    <t>0.158620553863444</t>
-  </si>
-  <si>
-    <t>1.05515169153752e-11</t>
-  </si>
-  <si>
-    <t>1.12259537863602e-09</t>
-  </si>
-  <si>
-    <t>3.26650689203036e-06</t>
-  </si>
-  <si>
-    <t>2.12141203910118e-11</t>
-  </si>
-  <si>
-    <t>0.00993299770097923</t>
-  </si>
-  <si>
-    <t>0.000385099079363515</t>
-  </si>
-  <si>
-    <t>3.1125703377813e-07</t>
-  </si>
-  <si>
-    <t>0.349795914040648</t>
-  </si>
-  <si>
-    <t>0.048727930753302</t>
-  </si>
-  <si>
-    <t>2.22521563614034e-09</t>
-  </si>
-  <si>
-    <t>0.000247067016510193</t>
-  </si>
-  <si>
-    <t>0.00745094102113636</t>
-  </si>
-  <si>
-    <t>6.82761032631197e-06</t>
-  </si>
-  <si>
-    <t>0.0601983692128174</t>
-  </si>
-  <si>
-    <t>0.00682456170074117</t>
-  </si>
-  <si>
-    <t>1.20761411476344e-06</t>
-  </si>
-  <si>
-    <t>0.955962910457758</t>
-  </si>
-  <si>
-    <t>0.401219231001671</t>
-  </si>
-  <si>
-    <t>0.365168956762468</t>
-  </si>
-  <si>
-    <t>0.000110703282610506</t>
-  </si>
-  <si>
-    <t>0.74903014746103</t>
-  </si>
-  <si>
-    <t>0.256369191335779</t>
-  </si>
-  <si>
-    <t>0.00312736546780098</t>
-  </si>
-  <si>
-    <t>0.010256951608853</t>
-  </si>
-  <si>
-    <t>0.0607064482641128</t>
-  </si>
-  <si>
-    <t>0.00381826521586663</t>
-  </si>
-  <si>
-    <t>0.16914107741446</t>
-  </si>
-  <si>
-    <t>0.805639865269386</t>
-  </si>
-  <si>
-    <t>0.261477829271621</t>
-  </si>
-  <si>
-    <t>0.024775995000882</t>
-  </si>
-  <si>
-    <t>0.678010318298413</t>
-  </si>
-  <si>
-    <t>0.0313920639967057</t>
-  </si>
-  <si>
-    <t>0.206290147097425</t>
-  </si>
-  <si>
-    <t>0.0155052242811367</t>
-  </si>
-  <si>
-    <t>0.711832372926219</t>
-  </si>
-  <si>
-    <t>0.00193540191429947</t>
-  </si>
-  <si>
-    <t>0.0493510012233794</t>
-  </si>
-  <si>
-    <t>9.7187165753135e-05</t>
-  </si>
-  <si>
-    <t>0.0036908364153514</t>
-  </si>
-  <si>
-    <t>0.0227511205462882</t>
-  </si>
-  <si>
-    <t>0.000182049797583368</t>
-  </si>
-  <si>
-    <t>0.00493126363918181</t>
-  </si>
-  <si>
-    <t>0.0001590938438404</t>
-  </si>
-  <si>
-    <t>3.44517178980373e-07</t>
-  </si>
-  <si>
-    <t>3.82476481191713e-06</t>
-  </si>
-  <si>
-    <t>0.00031079898518033</t>
-  </si>
-  <si>
-    <t>5.19489978704722e-07</t>
-  </si>
-  <si>
-    <t>0.233523145318151</t>
-  </si>
-  <si>
-    <t>0.032326247742665</t>
-  </si>
-  <si>
-    <t>0.000392693157836954</t>
-  </si>
-  <si>
-    <t>0.260688489825884</t>
-  </si>
-  <si>
-    <t>1.22212447174486e-05</t>
-  </si>
-  <si>
-    <t>0.0621682534353365</t>
-  </si>
-  <si>
-    <t>0.313696325308661</t>
-  </si>
-  <si>
-    <t>0.00979917051809948</t>
-  </si>
-  <si>
-    <t>0.723928810332315</t>
-  </si>
-  <si>
-    <t>0.260781194813724</t>
-  </si>
-  <si>
-    <t>0.00358239515124996</t>
-  </si>
-  <si>
-    <t>0.283261793873039</t>
-  </si>
-  <si>
-    <t>0.87308290920969</t>
-  </si>
-  <si>
-    <t>0.0151111273561674</t>
-  </si>
-  <si>
-    <t>0.224250393322217</t>
-  </si>
-  <si>
-    <t>0.328894663980921</t>
-  </si>
-  <si>
-    <t>0.0176884581992304</t>
-  </si>
-  <si>
-    <t>3.53130108454882e-07</t>
-  </si>
-  <si>
-    <t>3.88547536448724e-06</t>
-  </si>
-  <si>
-    <t>0.00031370364859323</t>
-  </si>
-  <si>
-    <t>5.31034200453716e-07</t>
-  </si>
-  <si>
-    <t>0.234453516415036</t>
-  </si>
-  <si>
-    <t>0.0324903403708004</t>
-  </si>
-  <si>
-    <t>0.000396230934033683</t>
-  </si>
-  <si>
-    <t>0.261687296300313</t>
-  </si>
-  <si>
-    <t>1.23863966730898e-05</t>
-  </si>
-  <si>
-    <t>0.0624574081024776</t>
-  </si>
-  <si>
-    <t>0.31481666932762</t>
-  </si>
-  <si>
-    <t>0.00985928812863997</t>
-  </si>
-  <si>
-    <t>0.72624168193082</t>
-  </si>
-  <si>
-    <t>0.261772758292104</t>
-  </si>
-  <si>
-    <t>0.00360780220906024</t>
-  </si>
-  <si>
-    <t>0.284307040344895</t>
-  </si>
-  <si>
-    <t>0.875761077642848</t>
-  </si>
-  <si>
-    <t>0.0151984749131395</t>
-  </si>
-  <si>
-    <t>0.225154628779161</t>
-  </si>
-  <si>
-    <t>0.330056835938451</t>
-  </si>
-  <si>
-    <t>0.0177867274114483</t>
-  </si>
-  <si>
-    <t>0.0226625892756562</t>
-  </si>
-  <si>
-    <t>0.0509494648801283</t>
-  </si>
-  <si>
-    <t>0.167279911169285</t>
-  </si>
-  <si>
-    <t>0.0264159896340754</t>
-  </si>
-  <si>
-    <t>0.0249439300537363</t>
-  </si>
-  <si>
-    <t>0.31397048932837</t>
-  </si>
-  <si>
-    <t>0.69253931476593</t>
-  </si>
-  <si>
-    <t>0.00367511536796807</t>
-  </si>
-  <si>
-    <t>0.365624125683063</t>
-  </si>
-  <si>
-    <t>0.147881461950181</t>
-  </si>
-  <si>
-    <t>0.0150295925968769</t>
-  </si>
-  <si>
-    <t>0.000245600656416685</t>
-  </si>
-  <si>
-    <t>0.15296723605969</t>
-  </si>
-  <si>
-    <t>1.38999712766552e-05</t>
-  </si>
-  <si>
-    <t>0.00245098773909985</t>
-  </si>
-  <si>
-    <t>0.30967112209388</t>
-  </si>
-  <si>
-    <t>2.36458530738246e-06</t>
-  </si>
-  <si>
-    <t>0.000197868905914505</t>
-  </si>
-  <si>
-    <t>0.00335125505612979</t>
-  </si>
-  <si>
-    <t>0.523324499413928</t>
-  </si>
-  <si>
-    <t>8.55459597836879e-06</t>
-  </si>
-  <si>
-    <t>0.000220971031909602</t>
-  </si>
-  <si>
-    <t>4.21521972147283e-06</t>
-  </si>
-  <si>
-    <t>0.513941625900634</t>
-  </si>
-  <si>
-    <t>0.00217382617227326</t>
-  </si>
-  <si>
-    <t>0.00219054791205998</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="347">
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C. purpurata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuscuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grammica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ipomoea nil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monogynella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haustorium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seedling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46224451926888e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75484851835537e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00322478514804319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72032065263047e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000682800230446674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0035853107459584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0337424317618012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000946866578579858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273797790863862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0639842341504868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121636143927188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270577440900021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0725333286055547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00482992735951079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137475031612282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47097950776123e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07032927025925e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000460400327310872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11978566589768e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260711948605843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0426950141993282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000812066078919599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0242542531115658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0326718615602025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0682399260355361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0253810619291163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747161188055441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805296150960781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248140300967333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270475818247867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530169016260407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601727280265683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715408972747075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542534833769019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000124537132673083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0113553785340147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295310767671895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60403805117689e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0708281954149198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39412010863675e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96830318319785e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00305740312859448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52935462450762e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618172914054875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354970425522269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00105667010131659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0863063636144745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928545186488749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75945517003654e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08222227784671e-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00041042491186e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000255894990943642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20449604609997e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571517418501662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0378053388696402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40128035655464e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351700211712042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521767683778997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6613157015166e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00457616268253145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72199492168867e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000131350929853924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0152035609481612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77612330536753e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131552358360585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0262818412814172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0168185109680361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79962028927607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000347256186511562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0208140162214639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67657227515035e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16259318542139e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1850061237932e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47637707085502e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90910229660792e-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167408645414639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00506315070110156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91277748286349e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747930276947236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290785232601444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77336958439926e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79574277838788e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1087268104732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35955817329655e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91637528332398e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21175833462657e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000712365883286905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11895842291517e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800575924110083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105739707082462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00013707569732857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292424068289888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626116350484326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436374305867e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17071859982009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713996372371247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00284655662765445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118127855377932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53517511318093e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000530900968184607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0291495608465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42200803310946e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045143467045902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.746760588338337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0799855778251784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00701363182218485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658060551524371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00176532299133625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000454912521722661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50903578058083e-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292183401966117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23238648557227e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000164671694831804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29517444158324e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32384811146346e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14020580866425e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44754678691524e-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00680034311564503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000235552287604985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54909547545767e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302786377256755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0398461142578602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08130449890359e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000132267191052863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00459610250181658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23260753572081e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0408509225109615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00427100957637709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.265267887922e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2668714614188e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04858613298135e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1566950977827e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93133086249473e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104913902714394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00788569009490001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87432059487337e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876351838786783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178982716905263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87683508876676e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0104040463903407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131055597929021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000594548340377815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45408889174505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104825595798068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000132183015817012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336473404241388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24583199074703e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13538982166457e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000422277068703477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76887765389534e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248715557993255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0395972784489365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000707386940368675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260644352335804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07070654414617e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078782147332221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33177300082611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0150505102797091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723133667997695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276582345707604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00620822277788642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314699178785733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902676513892812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00279824676031349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00980658026402619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0609258017453342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00354927107955494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150966706020696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779002291139313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262576304927262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0213698721704374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662406455712772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0302471103389535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171332083545665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0104455139133138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668820986575216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00107779619319593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0385317347256017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980578166727473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42333057935755e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00292638904999341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0194576661866949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36871686043055e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25148243921976e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31934835347203e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84495444937986e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00745204038665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000398361835084255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01222354320063e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241075240605813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0315293043051818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50679182019293e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000432447971566475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00705015762429371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76038881614787e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0400883856671761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00606925648662256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49044693113735e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817621083701603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260160775954813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.252049791564807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000134099135523838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94074037949834e-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81827085592423e-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32760463236945e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12202607884442e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151443071695378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010745958927152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67839085728675e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.235045951589767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86550660373235e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0128372525746945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.192144287095634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000510466173422112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661425144720851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153145649878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11621418027915e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.208211166054674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823400895912742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00370715601822831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158620553863444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05515169153752e-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12259537863602e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26650689203036e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12141203910118e-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00993299770097923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000385099079363515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1125703377813e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349795914040648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048727930753302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22521563614034e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000247067016510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00745094102113636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82761032631197e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0601983692128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00682456170074117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20761411476344e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955962910457758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401219231001671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365168956762468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000110703282610506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74903014746103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256369191335779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00312736546780098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010256951608853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0607064482641128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00381826521586663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16914107741446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805639865269386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261477829271621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024775995000882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678010318298413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0313920639967057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.206290147097425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0155052242811367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711832372926219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00193540191429947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0493510012233794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7187165753135e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0036908364153514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0227511205462882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000182049797583368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00493126363918181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0001590938438404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44517178980373e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82476481191713e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00031079898518033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19489978704722e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.233523145318151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032326247742665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000392693157836954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260688489825884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22212447174486e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0621682534353365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313696325308661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00979917051809948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723928810332315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260781194813724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00358239515124996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283261793873039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87308290920969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0151111273561674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.224250393322217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328894663980921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0176884581992304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53130108454882e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88547536448724e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00031370364859323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31034200453716e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234453516415036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0324903403708004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000396230934033683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261687296300313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23863966730898e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0624574081024776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31481666932762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00985928812863997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72624168193082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261772758292104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00360780220906024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284307040344895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875761077642848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0151984749131395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.225154628779161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330056835938451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0177867274114483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0226625892756562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0509494648801283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167279911169285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0264159896340754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0249439300537363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31397048932837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69253931476593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00367511536796807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365624125683063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147881461950181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0150295925968769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000245600656416685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15296723605969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38999712766552e-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00245098773909985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30967112209388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36458530738246e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000197868905914505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00335125505612979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523324499413928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55459597836879e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000220971031909602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21521972147283e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513941625900634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00217382617227326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00219054791205998</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1103,15 +1096,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1393,14 +1377,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1"/>
       <c r="C1" t="s">
         <v>1</v>
       </c>
@@ -1483,7 +1468,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
       <c r="C2" t="s">
         <v>6</v>
       </c>
@@ -1566,7 +1553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1655,7 +1642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1744,7 +1731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1833,7 +1820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1922,7 +1909,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -2011,7 +1998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -2100,7 +2087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2189,7 +2176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -2278,7 +2265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -2367,7 +2354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -2456,7 +2443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2545,7 +2532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2634,7 +2621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2723,7 +2710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2812,7 +2799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2901,7 +2888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2990,7 +2977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -3079,7 +3066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -3168,7 +3155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -3257,7 +3244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -3346,7 +3333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -3435,7 +3422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3524,7 +3511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3613,7 +3600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3702,7 +3689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3791,7 +3778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -3880,7 +3867,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3971,6 +3958,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>